--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/08_BIBS_UXScreens_BRD-11_User_Access_Maintenance_v2.1.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-11_User_Access_Maintenance/08_BIBS_UXScreens_BRD-11_User_Access_Maintenance_v2.1.xlsx
@@ -7205,7 +7205,7 @@
       </c>
       <c r="K99" s="45" t="inlineStr">
         <is>
-          <t>User Access Matrix (Excel): first page as generated</t>
+          <t>User Access Matrix (Excel): extract – the header of the workbook and the permissions of the User Access area against the group profiles UAM_REQUESTOR, UAM_APPROVER, UAM_SECOND_APPROVER, INFOSEC_OFFICER, SYSADMIN and AUDITOR (the full matrix: 293 permissions x 94 group profiles in the SIT/UAT data)</t>
         </is>
       </c>
       <c r="L99" s="45" t="inlineStr">
